--- a/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
@@ -21,12 +21,18 @@
     <x:t>From Strings</x:t>
   </x:si>
   <x:si>
+    <x:t>String</x:t>
+  </x:si>
+  <x:si>
+    <x:t>House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Car</x:t>
+  </x:si>
+  <x:si>
     <x:t>From Arrays</x:t>
   </x:si>
   <x:si>
-    <x:t>String</x:t>
-  </x:si>
-  <x:si>
     <x:t>Column1</x:t>
   </x:si>
   <x:si>
@@ -45,30 +51,54 @@
     <x:t>Column6</x:t>
   </x:si>
   <x:si>
-    <x:t>House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Car</x:t>
-  </x:si>
-  <x:si>
     <x:t>From DataTable</x:t>
   </x:si>
   <x:si>
+    <x:t>Dosage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Drug</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Patient</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Indocin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>David</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enebrel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sam</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hydralazine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Christoff</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Combivent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dilantin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Melanie</x:t>
+  </x:si>
+  <x:si>
     <x:t>From Query</x:t>
   </x:si>
   <x:si>
-    <x:t>Dosage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Drug</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Patient</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Date</x:t>
-  </x:si>
-  <x:si>
     <x:t>House Street</x:t>
   </x:si>
   <x:si>
@@ -81,12 +111,6 @@
     <x:t>Age</x:t>
   </x:si>
   <x:si>
-    <x:t>Indocin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>David</x:t>
-  </x:si>
-  <x:si>
     <x:t>On Elm St.</x:t>
   </x:si>
   <x:si>
@@ -96,40 +120,16 @@
     <x:t>John</x:t>
   </x:si>
   <x:si>
-    <x:t>Enebrel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sam</x:t>
-  </x:si>
-  <x:si>
     <x:t>On 23rd St.</x:t>
   </x:si>
   <x:si>
     <x:t>Luis</x:t>
   </x:si>
   <x:si>
-    <x:t>Hydralazine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Christoff</x:t>
-  </x:si>
-  <x:si>
     <x:t>On 5th Ave.</x:t>
   </x:si>
   <x:si>
     <x:t>Henry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Combivent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Janet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dilantin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Melanie</x:t>
   </x:si>
   <x:si>
     <x:t>From List</x:t>
@@ -596,7 +596,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="1"/>
@@ -606,30 +606,30 @@
     </x:row>
     <x:row r="2" spans="1:9">
       <x:c r="A2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>1</x:v>
@@ -643,7 +643,7 @@
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>1</x:v>
@@ -677,7 +677,7 @@
       <x:c r="C7" s="1"/>
       <x:c r="D7" s="1"/>
       <x:c r="F7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G7" s="1"/>
       <x:c r="H7" s="1"/>
@@ -685,28 +685,28 @@
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="C8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="D8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -714,22 +714,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="2">
         <x:v>36526</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>30</x:v>
@@ -740,22 +740,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="2">
         <x:v>36527</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>21</x:v>
@@ -766,22 +766,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D11" s="2">
         <x:v>36528</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>45</x:v>
@@ -792,10 +792,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D12" s="2">
         <x:v>36529</x:v>
@@ -806,10 +806,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="2">
         <x:v>36530</x:v>
@@ -825,27 +825,27 @@
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="F16" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="F17" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>30</x:v>
@@ -853,13 +853,13 @@
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="F18" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>21</x:v>
@@ -867,13 +867,13 @@
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="F19" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>45</x:v>

--- a/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
@@ -576,19 +576,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:I19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.567768" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="5" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.424911" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="6.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.567768" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
+    <x:col min="3" max="5" width="11.282054" customWidth="1"/>
+    <x:col min="6" max="6" width="14.996339" customWidth="1"/>
+    <x:col min="7" max="7" width="12.424911" customWidth="1"/>
+    <x:col min="8" max="8" width="11.282054" customWidth="1"/>
+    <x:col min="9" max="9" width="6.567768" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -605,67 +602,67 @@
       <x:c r="H1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:9">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="F2" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="G2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
+      <x:c r="H2" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F5" s="0">
+      <x:c r="F5">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G5" s="0">
+      <x:c r="G5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H5" s="0">
+      <x:c r="H5">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -684,117 +681,117 @@
       <x:c r="I7" s="1"/>
     </x:row>
     <x:row r="8" spans="1:9">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="A8" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="B8" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="C8" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="D8" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="s">
+      <x:c r="F8" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="G8" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
+      <x:c r="H8" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I8" s="0" t="s">
+      <x:c r="I8" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
-      <x:c r="A9" s="0">
+      <x:c r="A9">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="B9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="C9" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="2">
         <x:v>36526</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
+      <x:c r="F9" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
+      <x:c r="G9" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
+      <x:c r="H9" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I9" s="0">
+      <x:c r="I9">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
-      <x:c r="A10" s="0">
+      <x:c r="A10">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="B10" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
+      <x:c r="C10" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="2">
         <x:v>36527</x:v>
       </x:c>
-      <x:c r="F10" s="0" t="s">
+      <x:c r="F10" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G10" s="0" t="s">
+      <x:c r="G10" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
+      <x:c r="H10" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="I10" s="0">
+      <x:c r="I10">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
-      <x:c r="A11" s="0">
+      <x:c r="A11">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="B11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="C11" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D11" s="2">
         <x:v>36528</x:v>
       </x:c>
-      <x:c r="F11" s="0" t="s">
+      <x:c r="F11" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
+      <x:c r="G11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H11" s="0" t="s">
+      <x:c r="H11" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="I11" s="0">
+      <x:c r="I11">
         <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
-      <x:c r="A12" s="0">
+      <x:c r="A12">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="B12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="C12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D12" s="2">
@@ -802,13 +799,13 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
-      <x:c r="A13" s="0">
+      <x:c r="A13">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="B13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
+      <x:c r="C13" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="2">
@@ -824,58 +821,58 @@
       <x:c r="I15" s="1"/>
     </x:row>
     <x:row r="16" spans="1:9">
-      <x:c r="F16" s="0" t="s">
+      <x:c r="F16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G16" s="0" t="s">
+      <x:c r="G16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H16" s="0" t="s">
+      <x:c r="H16" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I16" s="0" t="s">
+      <x:c r="I16" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
-      <x:c r="F17" s="0" t="s">
+      <x:c r="F17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G17" s="0" t="s">
+      <x:c r="G17" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H17" s="0" t="s">
+      <x:c r="H17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I17" s="0">
+      <x:c r="I17">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
-      <x:c r="F18" s="0" t="s">
+      <x:c r="F18" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G18" s="0" t="s">
+      <x:c r="G18" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H18" s="0" t="s">
+      <x:c r="H18" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="I18" s="0">
+      <x:c r="I18">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
-      <x:c r="F19" s="0" t="s">
+      <x:c r="F19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G19" s="0" t="s">
+      <x:c r="G19" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H19" s="0" t="s">
+      <x:c r="H19" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="I19" s="0">
+      <x:c r="I19">
         <x:v>45</x:v>
       </x:c>
     </x:row>
@@ -886,10 +883,7 @@
     <x:mergeCell ref="F7:I7"/>
     <x:mergeCell ref="F15:I15"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="5">
     <x:tablePart r:id="rId5"/>
     <x:tablePart r:id="rId6"/>

--- a/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
@@ -579,12 +579,12 @@
   <x:dimension ref="A1:I19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.567768" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
-    <x:col min="3" max="5" width="11.282054" customWidth="1"/>
-    <x:col min="6" max="6" width="14.996339" customWidth="1"/>
-    <x:col min="7" max="7" width="12.424911" customWidth="1"/>
-    <x:col min="8" max="8" width="11.282054" customWidth="1"/>
+    <x:col min="1" max="1" width="11.996339" customWidth="1"/>
+    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
+    <x:col min="3" max="5" width="10.996339" customWidth="1"/>
+    <x:col min="6" max="6" width="14.424911" customWidth="1"/>
+    <x:col min="7" max="7" width="12.139196" customWidth="1"/>
+    <x:col min="8" max="8" width="10.996339" customWidth="1"/>
     <x:col min="9" max="9" width="6.567768" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
@@ -579,13 +579,13 @@
   <x:dimension ref="A1:I19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.996339" customWidth="1"/>
-    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
-    <x:col min="3" max="5" width="10.996339" customWidth="1"/>
-    <x:col min="6" max="6" width="14.424911" customWidth="1"/>
-    <x:col min="7" max="7" width="12.139196" customWidth="1"/>
-    <x:col min="8" max="8" width="10.996339" customWidth="1"/>
-    <x:col min="9" max="9" width="6.567768" customWidth="1"/>
+    <x:col min="1" max="1" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="11.142857" customWidth="1"/>
+    <x:col min="3" max="5" width="11" customWidth="1"/>
+    <x:col min="6" max="6" width="14.428571" customWidth="1"/>
+    <x:col min="7" max="7" width="12.142857" customWidth="1"/>
+    <x:col min="8" max="8" width="11" customWidth="1"/>
+    <x:col min="9" max="9" width="6.571429" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:9">
